--- a/hj/demo/demo/导入服务模板 (1).xlsx
+++ b/hj/demo/demo/导入服务模板 (1).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CD0CC3-DF4A-47B1-8A30-11C5EA90D6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE7F8B94-CB53-44BA-8A85-E1C34154C349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="350">
   <si>
     <t>代理服务名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1430,10 +1430,6 @@
   </si>
   <si>
     <t>http://172.16.238.67:8015/15290001122002/DGR2034/B_WBFFTMon</t>
-  </si>
-  <si>
-    <t>无线电管理员</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1946,9 +1942,6 @@
       <c r="I2" t="s">
         <v>96</v>
       </c>
-      <c r="J2" t="s">
-        <v>350</v>
-      </c>
       <c r="K2">
         <v>13947396696</v>
       </c>
@@ -1994,9 +1987,6 @@
       <c r="I3" t="s">
         <v>96</v>
       </c>
-      <c r="J3" t="s">
-        <v>350</v>
-      </c>
       <c r="K3">
         <v>13947396696</v>
       </c>
@@ -2041,9 +2031,6 @@
       <c r="I4" t="s">
         <v>96</v>
       </c>
-      <c r="J4" t="s">
-        <v>350</v>
-      </c>
       <c r="K4">
         <v>13947396696</v>
       </c>
@@ -2088,9 +2075,6 @@
       <c r="I5" t="s">
         <v>96</v>
       </c>
-      <c r="J5" t="s">
-        <v>350</v>
-      </c>
       <c r="K5">
         <v>13947396696</v>
       </c>
@@ -2135,9 +2119,6 @@
       <c r="I6" t="s">
         <v>96</v>
       </c>
-      <c r="J6" t="s">
-        <v>350</v>
-      </c>
       <c r="K6">
         <v>13947396696</v>
       </c>
@@ -2182,9 +2163,6 @@
       <c r="I7" t="s">
         <v>96</v>
       </c>
-      <c r="J7" t="s">
-        <v>350</v>
-      </c>
       <c r="K7">
         <v>13947396696</v>
       </c>
@@ -2229,9 +2207,6 @@
       <c r="I8" t="s">
         <v>96</v>
       </c>
-      <c r="J8" t="s">
-        <v>350</v>
-      </c>
       <c r="K8">
         <v>13947396696</v>
       </c>
@@ -2276,9 +2251,6 @@
       <c r="I9" t="s">
         <v>96</v>
       </c>
-      <c r="J9" t="s">
-        <v>350</v>
-      </c>
       <c r="K9">
         <v>13947396696</v>
       </c>
@@ -2323,9 +2295,6 @@
       <c r="I10" t="s">
         <v>96</v>
       </c>
-      <c r="J10" t="s">
-        <v>350</v>
-      </c>
       <c r="K10">
         <v>13947396696</v>
       </c>
@@ -2370,9 +2339,6 @@
       <c r="I11" t="s">
         <v>96</v>
       </c>
-      <c r="J11" t="s">
-        <v>350</v>
-      </c>
       <c r="K11">
         <v>13947396696</v>
       </c>
@@ -2417,9 +2383,6 @@
       <c r="I12" t="s">
         <v>96</v>
       </c>
-      <c r="J12" t="s">
-        <v>350</v>
-      </c>
       <c r="K12">
         <v>13947396696</v>
       </c>
@@ -2464,9 +2427,6 @@
       <c r="I13" t="s">
         <v>96</v>
       </c>
-      <c r="J13" t="s">
-        <v>350</v>
-      </c>
       <c r="K13">
         <v>13947396696</v>
       </c>
@@ -2511,9 +2471,6 @@
       <c r="I14" t="s">
         <v>96</v>
       </c>
-      <c r="J14" t="s">
-        <v>350</v>
-      </c>
       <c r="K14">
         <v>13947396696</v>
       </c>
@@ -2558,9 +2515,6 @@
       <c r="I15" t="s">
         <v>96</v>
       </c>
-      <c r="J15" t="s">
-        <v>350</v>
-      </c>
       <c r="K15">
         <v>13947396696</v>
       </c>
@@ -2605,9 +2559,6 @@
       <c r="I16" t="s">
         <v>96</v>
       </c>
-      <c r="J16" t="s">
-        <v>350</v>
-      </c>
       <c r="K16">
         <v>13947396696</v>
       </c>
@@ -2652,9 +2603,6 @@
       <c r="I17" t="s">
         <v>96</v>
       </c>
-      <c r="J17" t="s">
-        <v>350</v>
-      </c>
       <c r="K17">
         <v>13947396696</v>
       </c>
@@ -2699,9 +2647,6 @@
       <c r="I18" t="s">
         <v>96</v>
       </c>
-      <c r="J18" t="s">
-        <v>350</v>
-      </c>
       <c r="K18">
         <v>13947396696</v>
       </c>
@@ -2746,9 +2691,6 @@
       <c r="I19" t="s">
         <v>96</v>
       </c>
-      <c r="J19" t="s">
-        <v>350</v>
-      </c>
       <c r="K19">
         <v>13947396696</v>
       </c>
@@ -2793,9 +2735,6 @@
       <c r="I20" t="s">
         <v>96</v>
       </c>
-      <c r="J20" t="s">
-        <v>350</v>
-      </c>
       <c r="K20">
         <v>13947396696</v>
       </c>
@@ -2840,9 +2779,6 @@
       <c r="I21" t="s">
         <v>96</v>
       </c>
-      <c r="J21" t="s">
-        <v>350</v>
-      </c>
       <c r="K21">
         <v>13947396696</v>
       </c>
@@ -2887,9 +2823,6 @@
       <c r="I22" t="s">
         <v>96</v>
       </c>
-      <c r="J22" t="s">
-        <v>350</v>
-      </c>
       <c r="K22">
         <v>13947396696</v>
       </c>
@@ -2934,9 +2867,6 @@
       <c r="I23" t="s">
         <v>96</v>
       </c>
-      <c r="J23" t="s">
-        <v>350</v>
-      </c>
       <c r="K23">
         <v>13947396696</v>
       </c>
@@ -2981,9 +2911,6 @@
       <c r="I24" t="s">
         <v>96</v>
       </c>
-      <c r="J24" t="s">
-        <v>350</v>
-      </c>
       <c r="K24">
         <v>13947396696</v>
       </c>
@@ -3028,9 +2955,6 @@
       <c r="I25" t="s">
         <v>96</v>
       </c>
-      <c r="J25" t="s">
-        <v>350</v>
-      </c>
       <c r="K25">
         <v>13947396696</v>
       </c>
@@ -3075,9 +2999,6 @@
       <c r="I26" t="s">
         <v>96</v>
       </c>
-      <c r="J26" t="s">
-        <v>350</v>
-      </c>
       <c r="K26">
         <v>13947396696</v>
       </c>
@@ -3122,9 +3043,6 @@
       <c r="I27" t="s">
         <v>96</v>
       </c>
-      <c r="J27" t="s">
-        <v>350</v>
-      </c>
       <c r="K27">
         <v>13947396696</v>
       </c>
@@ -3169,9 +3087,6 @@
       <c r="I28" t="s">
         <v>96</v>
       </c>
-      <c r="J28" t="s">
-        <v>350</v>
-      </c>
       <c r="K28">
         <v>13947396696</v>
       </c>
@@ -3216,9 +3131,6 @@
       <c r="I29" t="s">
         <v>96</v>
       </c>
-      <c r="J29" t="s">
-        <v>350</v>
-      </c>
       <c r="K29">
         <v>13947396696</v>
       </c>
@@ -3263,9 +3175,6 @@
       <c r="I30" t="s">
         <v>96</v>
       </c>
-      <c r="J30" t="s">
-        <v>350</v>
-      </c>
       <c r="K30">
         <v>13947396696</v>
       </c>
@@ -3310,9 +3219,6 @@
       <c r="I31" t="s">
         <v>96</v>
       </c>
-      <c r="J31" t="s">
-        <v>350</v>
-      </c>
       <c r="K31">
         <v>13947396696</v>
       </c>
@@ -3357,9 +3263,6 @@
       <c r="I32" t="s">
         <v>84</v>
       </c>
-      <c r="J32" t="s">
-        <v>350</v>
-      </c>
       <c r="K32" s="8">
         <v>18604743099</v>
       </c>
@@ -3404,9 +3307,6 @@
       <c r="I33" t="s">
         <v>84</v>
       </c>
-      <c r="J33" t="s">
-        <v>350</v>
-      </c>
       <c r="K33" s="8">
         <v>18604743099</v>
       </c>
@@ -3451,9 +3351,6 @@
       <c r="I34" t="s">
         <v>84</v>
       </c>
-      <c r="J34" t="s">
-        <v>350</v>
-      </c>
       <c r="K34" s="8">
         <v>18604743099</v>
       </c>
@@ -3498,9 +3395,6 @@
       <c r="I35" t="s">
         <v>84</v>
       </c>
-      <c r="J35" t="s">
-        <v>350</v>
-      </c>
       <c r="K35" s="8">
         <v>18604743099</v>
       </c>
@@ -3545,9 +3439,6 @@
       <c r="I36" t="s">
         <v>84</v>
       </c>
-      <c r="J36" t="s">
-        <v>350</v>
-      </c>
       <c r="K36" s="8">
         <v>18604743099</v>
       </c>
@@ -3592,9 +3483,6 @@
       <c r="I37" t="s">
         <v>84</v>
       </c>
-      <c r="J37" t="s">
-        <v>350</v>
-      </c>
       <c r="K37" s="8">
         <v>18604743099</v>
       </c>
@@ -3639,9 +3527,6 @@
       <c r="I38" t="s">
         <v>84</v>
       </c>
-      <c r="J38" t="s">
-        <v>350</v>
-      </c>
       <c r="K38" s="8">
         <v>18604743099</v>
       </c>
@@ -3686,9 +3571,6 @@
       <c r="I39" t="s">
         <v>84</v>
       </c>
-      <c r="J39" t="s">
-        <v>350</v>
-      </c>
       <c r="K39" s="8">
         <v>18604743099</v>
       </c>
@@ -3733,9 +3615,6 @@
       <c r="I40" t="s">
         <v>84</v>
       </c>
-      <c r="J40" t="s">
-        <v>350</v>
-      </c>
       <c r="K40" s="8">
         <v>18604743099</v>
       </c>
@@ -3780,9 +3659,6 @@
       <c r="I41" t="s">
         <v>84</v>
       </c>
-      <c r="J41" t="s">
-        <v>350</v>
-      </c>
       <c r="K41" s="8">
         <v>18604743099</v>
       </c>
@@ -3827,9 +3703,6 @@
       <c r="I42" t="s">
         <v>84</v>
       </c>
-      <c r="J42" t="s">
-        <v>350</v>
-      </c>
       <c r="K42" s="8">
         <v>18604743099</v>
       </c>
@@ -3874,9 +3747,6 @@
       <c r="I43" t="s">
         <v>84</v>
       </c>
-      <c r="J43" t="s">
-        <v>350</v>
-      </c>
       <c r="K43" s="8">
         <v>18604743099</v>
       </c>
@@ -3921,9 +3791,6 @@
       <c r="I44" t="s">
         <v>84</v>
       </c>
-      <c r="J44" t="s">
-        <v>350</v>
-      </c>
       <c r="K44" s="8">
         <v>18604743099</v>
       </c>
@@ -3968,9 +3835,6 @@
       <c r="I45" t="s">
         <v>84</v>
       </c>
-      <c r="J45" t="s">
-        <v>350</v>
-      </c>
       <c r="K45" s="8">
         <v>18604743099</v>
       </c>
@@ -4015,9 +3879,6 @@
       <c r="I46" t="s">
         <v>84</v>
       </c>
-      <c r="J46" t="s">
-        <v>350</v>
-      </c>
       <c r="K46" s="8">
         <v>18604743099</v>
       </c>
@@ -4062,9 +3923,6 @@
       <c r="I47" t="s">
         <v>84</v>
       </c>
-      <c r="J47" t="s">
-        <v>350</v>
-      </c>
       <c r="K47" s="8">
         <v>18604743099</v>
       </c>
@@ -4109,9 +3967,6 @@
       <c r="I48" t="s">
         <v>84</v>
       </c>
-      <c r="J48" t="s">
-        <v>350</v>
-      </c>
       <c r="K48" s="8">
         <v>18604743099</v>
       </c>
@@ -4156,9 +4011,6 @@
       <c r="I49" t="s">
         <v>84</v>
       </c>
-      <c r="J49" t="s">
-        <v>350</v>
-      </c>
       <c r="K49" s="8">
         <v>18604743099</v>
       </c>
@@ -4203,9 +4055,6 @@
       <c r="I50" t="s">
         <v>84</v>
       </c>
-      <c r="J50" t="s">
-        <v>350</v>
-      </c>
       <c r="K50" s="8">
         <v>18604743099</v>
       </c>
@@ -4250,9 +4099,6 @@
       <c r="I51" t="s">
         <v>84</v>
       </c>
-      <c r="J51" t="s">
-        <v>350</v>
-      </c>
       <c r="K51" s="8">
         <v>18604743099</v>
       </c>
@@ -4297,9 +4143,6 @@
       <c r="I52" t="s">
         <v>84</v>
       </c>
-      <c r="J52" t="s">
-        <v>350</v>
-      </c>
       <c r="K52" s="8">
         <v>18604743099</v>
       </c>
@@ -4344,9 +4187,6 @@
       <c r="I53" t="s">
         <v>84</v>
       </c>
-      <c r="J53" t="s">
-        <v>350</v>
-      </c>
       <c r="K53" s="8">
         <v>18604743099</v>
       </c>
@@ -4391,9 +4231,6 @@
       <c r="I54" t="s">
         <v>84</v>
       </c>
-      <c r="J54" t="s">
-        <v>350</v>
-      </c>
       <c r="K54" s="8">
         <v>18604743099</v>
       </c>
@@ -4438,9 +4275,6 @@
       <c r="I55" t="s">
         <v>84</v>
       </c>
-      <c r="J55" t="s">
-        <v>350</v>
-      </c>
       <c r="K55" s="8">
         <v>18604743099</v>
       </c>
@@ -4485,9 +4319,6 @@
       <c r="I56" t="s">
         <v>84</v>
       </c>
-      <c r="J56" t="s">
-        <v>350</v>
-      </c>
       <c r="K56" s="8">
         <v>18604743099</v>
       </c>
@@ -4532,9 +4363,6 @@
       <c r="I57" t="s">
         <v>84</v>
       </c>
-      <c r="J57" t="s">
-        <v>350</v>
-      </c>
       <c r="K57" s="8">
         <v>18604743099</v>
       </c>
@@ -4579,9 +4407,6 @@
       <c r="I58" t="s">
         <v>84</v>
       </c>
-      <c r="J58" t="s">
-        <v>350</v>
-      </c>
       <c r="K58" s="8">
         <v>18604743099</v>
       </c>
@@ -4626,9 +4451,6 @@
       <c r="I59" t="s">
         <v>84</v>
       </c>
-      <c r="J59" t="s">
-        <v>350</v>
-      </c>
       <c r="K59" s="8">
         <v>18604743099</v>
       </c>
@@ -4673,9 +4495,6 @@
       <c r="I60" t="s">
         <v>84</v>
       </c>
-      <c r="J60" t="s">
-        <v>350</v>
-      </c>
       <c r="K60" s="8">
         <v>18604743099</v>
       </c>
@@ -4720,9 +4539,6 @@
       <c r="I61" t="s">
         <v>84</v>
       </c>
-      <c r="J61" t="s">
-        <v>350</v>
-      </c>
       <c r="K61" s="8">
         <v>18604743099</v>
       </c>
@@ -4767,9 +4583,6 @@
       <c r="I62" t="s">
         <v>84</v>
       </c>
-      <c r="J62" t="s">
-        <v>350</v>
-      </c>
       <c r="K62" s="8">
         <v>18604743099</v>
       </c>
@@ -4814,9 +4627,6 @@
       <c r="I63" t="s">
         <v>84</v>
       </c>
-      <c r="J63" t="s">
-        <v>350</v>
-      </c>
       <c r="K63" s="8">
         <v>18604743099</v>
       </c>
@@ -4861,9 +4671,6 @@
       <c r="I64" t="s">
         <v>80</v>
       </c>
-      <c r="J64" t="s">
-        <v>350</v>
-      </c>
       <c r="K64" s="8">
         <v>13312341234</v>
       </c>
@@ -4908,9 +4715,6 @@
       <c r="I65" t="s">
         <v>80</v>
       </c>
-      <c r="J65" t="s">
-        <v>350</v>
-      </c>
       <c r="K65" s="8">
         <v>13312341234</v>
       </c>
@@ -4955,9 +4759,6 @@
       <c r="I66" t="s">
         <v>80</v>
       </c>
-      <c r="J66" t="s">
-        <v>350</v>
-      </c>
       <c r="K66" s="8">
         <v>13312341234</v>
       </c>
@@ -5002,9 +4803,6 @@
       <c r="I67" t="s">
         <v>80</v>
       </c>
-      <c r="J67" t="s">
-        <v>350</v>
-      </c>
       <c r="K67" s="8">
         <v>13312341234</v>
       </c>
@@ -5049,9 +4847,6 @@
       <c r="I68" t="s">
         <v>80</v>
       </c>
-      <c r="J68" t="s">
-        <v>350</v>
-      </c>
       <c r="K68" s="8">
         <v>13312341234</v>
       </c>
@@ -5096,9 +4891,6 @@
       <c r="I69" t="s">
         <v>80</v>
       </c>
-      <c r="J69" t="s">
-        <v>350</v>
-      </c>
       <c r="K69" s="8">
         <v>13312341234</v>
       </c>
@@ -5143,9 +4935,6 @@
       <c r="I70" t="s">
         <v>80</v>
       </c>
-      <c r="J70" t="s">
-        <v>350</v>
-      </c>
       <c r="K70" s="8">
         <v>13312341234</v>
       </c>
@@ -5190,9 +4979,6 @@
       <c r="I71" t="s">
         <v>80</v>
       </c>
-      <c r="J71" t="s">
-        <v>350</v>
-      </c>
       <c r="K71" s="8">
         <v>13312341234</v>
       </c>
@@ -5237,9 +5023,6 @@
       <c r="I72" t="s">
         <v>80</v>
       </c>
-      <c r="J72" t="s">
-        <v>350</v>
-      </c>
       <c r="K72" s="8">
         <v>13312341234</v>
       </c>
@@ -5284,9 +5067,6 @@
       <c r="I73" t="s">
         <v>80</v>
       </c>
-      <c r="J73" t="s">
-        <v>350</v>
-      </c>
       <c r="K73" s="8">
         <v>13312341234</v>
       </c>
@@ -5331,9 +5111,6 @@
       <c r="I74" t="s">
         <v>80</v>
       </c>
-      <c r="J74" t="s">
-        <v>350</v>
-      </c>
       <c r="K74" s="8">
         <v>13312341234</v>
       </c>
@@ -5378,9 +5155,6 @@
       <c r="I75" t="s">
         <v>80</v>
       </c>
-      <c r="J75" t="s">
-        <v>350</v>
-      </c>
       <c r="K75" s="8">
         <v>13312341234</v>
       </c>
@@ -5425,9 +5199,6 @@
       <c r="I76" t="s">
         <v>80</v>
       </c>
-      <c r="J76" t="s">
-        <v>350</v>
-      </c>
       <c r="K76" s="8">
         <v>13312341234</v>
       </c>
@@ -5472,9 +5243,6 @@
       <c r="I77" t="s">
         <v>80</v>
       </c>
-      <c r="J77" t="s">
-        <v>350</v>
-      </c>
       <c r="K77" s="8">
         <v>13312341234</v>
       </c>
@@ -5519,9 +5287,6 @@
       <c r="I78" t="s">
         <v>80</v>
       </c>
-      <c r="J78" t="s">
-        <v>350</v>
-      </c>
       <c r="K78" s="8">
         <v>13312341234</v>
       </c>
@@ -5566,9 +5331,6 @@
       <c r="I79" t="s">
         <v>80</v>
       </c>
-      <c r="J79" t="s">
-        <v>350</v>
-      </c>
       <c r="K79" s="8">
         <v>13312341234</v>
       </c>
@@ -5613,9 +5375,6 @@
       <c r="I80" t="s">
         <v>80</v>
       </c>
-      <c r="J80" t="s">
-        <v>350</v>
-      </c>
       <c r="K80" s="8">
         <v>13312341234</v>
       </c>
@@ -5660,9 +5419,6 @@
       <c r="I81" t="s">
         <v>80</v>
       </c>
-      <c r="J81" t="s">
-        <v>350</v>
-      </c>
       <c r="K81" s="8">
         <v>13312341234</v>
       </c>
@@ -5707,9 +5463,6 @@
       <c r="I82" t="s">
         <v>80</v>
       </c>
-      <c r="J82" t="s">
-        <v>350</v>
-      </c>
       <c r="K82" s="8">
         <v>13312341234</v>
       </c>
@@ -5754,9 +5507,6 @@
       <c r="I83" t="s">
         <v>80</v>
       </c>
-      <c r="J83" t="s">
-        <v>350</v>
-      </c>
       <c r="K83" s="8">
         <v>13312341234</v>
       </c>
@@ -5801,9 +5551,6 @@
       <c r="I84" t="s">
         <v>80</v>
       </c>
-      <c r="J84" t="s">
-        <v>350</v>
-      </c>
       <c r="K84" s="8">
         <v>13312341234</v>
       </c>
@@ -5848,9 +5595,6 @@
       <c r="I85" t="s">
         <v>80</v>
       </c>
-      <c r="J85" t="s">
-        <v>350</v>
-      </c>
       <c r="K85" s="8">
         <v>13312341234</v>
       </c>
@@ -5895,9 +5639,6 @@
       <c r="I86" t="s">
         <v>80</v>
       </c>
-      <c r="J86" t="s">
-        <v>350</v>
-      </c>
       <c r="K86" s="8">
         <v>13312341234</v>
       </c>
@@ -5942,9 +5683,6 @@
       <c r="I87" t="s">
         <v>80</v>
       </c>
-      <c r="J87" t="s">
-        <v>350</v>
-      </c>
       <c r="K87" s="8">
         <v>13312341234</v>
       </c>
@@ -5989,9 +5727,6 @@
       <c r="I88" t="s">
         <v>80</v>
       </c>
-      <c r="J88" t="s">
-        <v>350</v>
-      </c>
       <c r="K88" s="8">
         <v>13312341234</v>
       </c>
@@ -6036,9 +5771,6 @@
       <c r="I89" t="s">
         <v>80</v>
       </c>
-      <c r="J89" t="s">
-        <v>350</v>
-      </c>
       <c r="K89" s="8">
         <v>13312341234</v>
       </c>
@@ -6083,9 +5815,6 @@
       <c r="I90" t="s">
         <v>80</v>
       </c>
-      <c r="J90" t="s">
-        <v>350</v>
-      </c>
       <c r="K90" s="8">
         <v>13312341234</v>
       </c>
@@ -6130,9 +5859,6 @@
       <c r="I91" t="s">
         <v>80</v>
       </c>
-      <c r="J91" t="s">
-        <v>350</v>
-      </c>
       <c r="K91" s="8">
         <v>13312341234</v>
       </c>
@@ -6177,9 +5903,6 @@
       <c r="I92" t="s">
         <v>80</v>
       </c>
-      <c r="J92" t="s">
-        <v>350</v>
-      </c>
       <c r="K92" s="8">
         <v>13312341234</v>
       </c>
@@ -6224,9 +5947,6 @@
       <c r="I93" t="s">
         <v>80</v>
       </c>
-      <c r="J93" t="s">
-        <v>350</v>
-      </c>
       <c r="K93" s="8">
         <v>13312341234</v>
       </c>
@@ -6271,9 +5991,6 @@
       <c r="I94" t="s">
         <v>80</v>
       </c>
-      <c r="J94" t="s">
-        <v>350</v>
-      </c>
       <c r="K94" s="8">
         <v>13312341234</v>
       </c>
@@ -6318,9 +6035,6 @@
       <c r="I95" t="s">
         <v>80</v>
       </c>
-      <c r="J95" t="s">
-        <v>350</v>
-      </c>
       <c r="K95" s="8">
         <v>13312341234</v>
       </c>
@@ -6365,9 +6079,6 @@
       <c r="I96" t="s">
         <v>80</v>
       </c>
-      <c r="J96" t="s">
-        <v>350</v>
-      </c>
       <c r="K96" s="8">
         <v>13312341234</v>
       </c>
@@ -6412,9 +6123,6 @@
       <c r="I97" t="s">
         <v>86</v>
       </c>
-      <c r="J97" t="s">
-        <v>350</v>
-      </c>
       <c r="K97" s="8">
         <v>17760578425</v>
       </c>
@@ -6459,9 +6167,6 @@
       <c r="I98" t="s">
         <v>86</v>
       </c>
-      <c r="J98" t="s">
-        <v>350</v>
-      </c>
       <c r="K98" s="8">
         <v>17760578425</v>
       </c>
@@ -6506,9 +6211,6 @@
       <c r="I99" t="s">
         <v>86</v>
       </c>
-      <c r="J99" t="s">
-        <v>350</v>
-      </c>
       <c r="K99" s="8">
         <v>17760578425</v>
       </c>
@@ -6553,9 +6255,6 @@
       <c r="I100" t="s">
         <v>86</v>
       </c>
-      <c r="J100" t="s">
-        <v>350</v>
-      </c>
       <c r="K100" s="8">
         <v>17760578425</v>
       </c>
@@ -6600,9 +6299,6 @@
       <c r="I101" t="s">
         <v>86</v>
       </c>
-      <c r="J101" t="s">
-        <v>350</v>
-      </c>
       <c r="K101" s="8">
         <v>17760578425</v>
       </c>
@@ -6647,9 +6343,6 @@
       <c r="I102" t="s">
         <v>86</v>
       </c>
-      <c r="J102" t="s">
-        <v>350</v>
-      </c>
       <c r="K102" s="8">
         <v>17760578425</v>
       </c>
@@ -6694,9 +6387,6 @@
       <c r="I103" t="s">
         <v>86</v>
       </c>
-      <c r="J103" t="s">
-        <v>350</v>
-      </c>
       <c r="K103" s="8">
         <v>17760578425</v>
       </c>
@@ -6741,9 +6431,6 @@
       <c r="I104" t="s">
         <v>86</v>
       </c>
-      <c r="J104" t="s">
-        <v>350</v>
-      </c>
       <c r="K104" s="8">
         <v>17760578425</v>
       </c>
@@ -6788,9 +6475,6 @@
       <c r="I105" t="s">
         <v>86</v>
       </c>
-      <c r="J105" t="s">
-        <v>350</v>
-      </c>
       <c r="K105" s="8">
         <v>17760578425</v>
       </c>
@@ -6835,9 +6519,6 @@
       <c r="I106" t="s">
         <v>86</v>
       </c>
-      <c r="J106" t="s">
-        <v>350</v>
-      </c>
       <c r="K106" s="8">
         <v>17760578425</v>
       </c>
@@ -6882,9 +6563,6 @@
       <c r="I107" t="s">
         <v>86</v>
       </c>
-      <c r="J107" t="s">
-        <v>350</v>
-      </c>
       <c r="K107" s="8">
         <v>17760578425</v>
       </c>
@@ -6929,9 +6607,6 @@
       <c r="I108" t="s">
         <v>86</v>
       </c>
-      <c r="J108" t="s">
-        <v>350</v>
-      </c>
       <c r="K108" s="8">
         <v>17760578425</v>
       </c>
@@ -6976,9 +6651,6 @@
       <c r="I109" t="s">
         <v>86</v>
       </c>
-      <c r="J109" t="s">
-        <v>350</v>
-      </c>
       <c r="K109" s="8">
         <v>17760578425</v>
       </c>
@@ -7023,9 +6695,6 @@
       <c r="I110" t="s">
         <v>86</v>
       </c>
-      <c r="J110" t="s">
-        <v>350</v>
-      </c>
       <c r="K110" s="8">
         <v>17760578425</v>
       </c>
@@ -7070,9 +6739,6 @@
       <c r="I111" t="s">
         <v>86</v>
       </c>
-      <c r="J111" t="s">
-        <v>350</v>
-      </c>
       <c r="K111" s="8">
         <v>17760578425</v>
       </c>
@@ -7117,9 +6783,6 @@
       <c r="I112" t="s">
         <v>86</v>
       </c>
-      <c r="J112" t="s">
-        <v>350</v>
-      </c>
       <c r="K112" s="8">
         <v>17760578425</v>
       </c>
@@ -7164,9 +6827,6 @@
       <c r="I113" t="s">
         <v>86</v>
       </c>
-      <c r="J113" t="s">
-        <v>350</v>
-      </c>
       <c r="K113" s="8">
         <v>17760578425</v>
       </c>
@@ -7211,9 +6871,6 @@
       <c r="I114" t="s">
         <v>86</v>
       </c>
-      <c r="J114" t="s">
-        <v>350</v>
-      </c>
       <c r="K114" s="8">
         <v>17760578425</v>
       </c>
@@ -7258,9 +6915,6 @@
       <c r="I115" t="s">
         <v>86</v>
       </c>
-      <c r="J115" t="s">
-        <v>350</v>
-      </c>
       <c r="K115" s="8">
         <v>17760578425</v>
       </c>
@@ -7305,9 +6959,6 @@
       <c r="I116" t="s">
         <v>86</v>
       </c>
-      <c r="J116" t="s">
-        <v>350</v>
-      </c>
       <c r="K116" s="8">
         <v>17760578425</v>
       </c>
@@ -7352,9 +7003,6 @@
       <c r="I117" t="s">
         <v>86</v>
       </c>
-      <c r="J117" t="s">
-        <v>350</v>
-      </c>
       <c r="K117" s="8">
         <v>17760578425</v>
       </c>
@@ -7399,9 +7047,6 @@
       <c r="I118" t="s">
         <v>86</v>
       </c>
-      <c r="J118" t="s">
-        <v>350</v>
-      </c>
       <c r="K118" s="8">
         <v>17760578425</v>
       </c>
@@ -7446,9 +7091,6 @@
       <c r="I119" t="s">
         <v>86</v>
       </c>
-      <c r="J119" t="s">
-        <v>350</v>
-      </c>
       <c r="K119" s="8">
         <v>17760578425</v>
       </c>
@@ -7493,9 +7135,6 @@
       <c r="I120" t="s">
         <v>86</v>
       </c>
-      <c r="J120" t="s">
-        <v>350</v>
-      </c>
       <c r="K120" s="8">
         <v>17760578425</v>
       </c>
@@ -7540,9 +7179,6 @@
       <c r="I121" t="s">
         <v>86</v>
       </c>
-      <c r="J121" t="s">
-        <v>350</v>
-      </c>
       <c r="K121" s="8">
         <v>17760578425</v>
       </c>
@@ -7587,9 +7223,6 @@
       <c r="I122" t="s">
         <v>86</v>
       </c>
-      <c r="J122" t="s">
-        <v>350</v>
-      </c>
       <c r="K122" s="8">
         <v>17760578425</v>
       </c>
@@ -7634,9 +7267,6 @@
       <c r="I123" t="s">
         <v>86</v>
       </c>
-      <c r="J123" t="s">
-        <v>350</v>
-      </c>
       <c r="K123" s="8">
         <v>17760578425</v>
       </c>
@@ -7681,9 +7311,6 @@
       <c r="I124" t="s">
         <v>86</v>
       </c>
-      <c r="J124" t="s">
-        <v>350</v>
-      </c>
       <c r="K124" s="8">
         <v>17760578425</v>
       </c>
@@ -7728,9 +7355,6 @@
       <c r="I125" t="s">
         <v>86</v>
       </c>
-      <c r="J125" t="s">
-        <v>350</v>
-      </c>
       <c r="K125" s="8">
         <v>17760578425</v>
       </c>
@@ -7775,9 +7399,6 @@
       <c r="I126" t="s">
         <v>86</v>
       </c>
-      <c r="J126" t="s">
-        <v>350</v>
-      </c>
       <c r="K126" s="8">
         <v>17760578425</v>
       </c>
@@ -7822,9 +7443,6 @@
       <c r="I127" t="s">
         <v>86</v>
       </c>
-      <c r="J127" t="s">
-        <v>350</v>
-      </c>
       <c r="K127" s="8">
         <v>17760578425</v>
       </c>
@@ -7869,9 +7487,6 @@
       <c r="I128" t="s">
         <v>86</v>
       </c>
-      <c r="J128" t="s">
-        <v>350</v>
-      </c>
       <c r="K128" s="8">
         <v>17760578425</v>
       </c>
@@ -7916,9 +7531,6 @@
       <c r="I129" t="s">
         <v>86</v>
       </c>
-      <c r="J129" t="s">
-        <v>350</v>
-      </c>
       <c r="K129" s="8">
         <v>17760578425</v>
       </c>
@@ -7963,9 +7575,6 @@
       <c r="I130" t="s">
         <v>85</v>
       </c>
-      <c r="J130" t="s">
-        <v>350</v>
-      </c>
       <c r="K130" s="8">
         <v>18004788111</v>
       </c>
@@ -8010,9 +7619,6 @@
       <c r="I131" t="s">
         <v>85</v>
       </c>
-      <c r="J131" t="s">
-        <v>350</v>
-      </c>
       <c r="K131" s="8">
         <v>18004788111</v>
       </c>
@@ -8057,9 +7663,6 @@
       <c r="I132" t="s">
         <v>85</v>
       </c>
-      <c r="J132" t="s">
-        <v>350</v>
-      </c>
       <c r="K132" s="8">
         <v>18004788111</v>
       </c>
@@ -8104,9 +7707,6 @@
       <c r="I133" t="s">
         <v>85</v>
       </c>
-      <c r="J133" t="s">
-        <v>350</v>
-      </c>
       <c r="K133" s="8">
         <v>18004788111</v>
       </c>
@@ -8151,9 +7751,6 @@
       <c r="I134" t="s">
         <v>85</v>
       </c>
-      <c r="J134" t="s">
-        <v>350</v>
-      </c>
       <c r="K134" s="8">
         <v>18004788111</v>
       </c>
@@ -8198,9 +7795,6 @@
       <c r="I135" t="s">
         <v>85</v>
       </c>
-      <c r="J135" t="s">
-        <v>350</v>
-      </c>
       <c r="K135" s="8">
         <v>18004788111</v>
       </c>
@@ -8245,9 +7839,6 @@
       <c r="I136" t="s">
         <v>85</v>
       </c>
-      <c r="J136" t="s">
-        <v>350</v>
-      </c>
       <c r="K136" s="8">
         <v>18004788111</v>
       </c>
@@ -8292,9 +7883,6 @@
       <c r="I137" t="s">
         <v>85</v>
       </c>
-      <c r="J137" t="s">
-        <v>350</v>
-      </c>
       <c r="K137" s="8">
         <v>18004788111</v>
       </c>
@@ -8339,9 +7927,6 @@
       <c r="I138" t="s">
         <v>85</v>
       </c>
-      <c r="J138" t="s">
-        <v>350</v>
-      </c>
       <c r="K138" s="8">
         <v>18004788111</v>
       </c>
@@ -8386,9 +7971,6 @@
       <c r="I139" t="s">
         <v>85</v>
       </c>
-      <c r="J139" t="s">
-        <v>350</v>
-      </c>
       <c r="K139" s="8">
         <v>18004788111</v>
       </c>
@@ -8433,9 +8015,6 @@
       <c r="I140" t="s">
         <v>85</v>
       </c>
-      <c r="J140" t="s">
-        <v>350</v>
-      </c>
       <c r="K140" s="8">
         <v>18004788111</v>
       </c>
@@ -8480,9 +8059,6 @@
       <c r="I141" t="s">
         <v>85</v>
       </c>
-      <c r="J141" t="s">
-        <v>350</v>
-      </c>
       <c r="K141" s="8">
         <v>18004788111</v>
       </c>
@@ -8527,9 +8103,6 @@
       <c r="I142" t="s">
         <v>85</v>
       </c>
-      <c r="J142" t="s">
-        <v>350</v>
-      </c>
       <c r="K142" s="8">
         <v>18004788111</v>
       </c>
@@ -8574,9 +8147,6 @@
       <c r="I143" t="s">
         <v>85</v>
       </c>
-      <c r="J143" t="s">
-        <v>350</v>
-      </c>
       <c r="K143" s="8">
         <v>18004788111</v>
       </c>
@@ -8621,9 +8191,6 @@
       <c r="I144" t="s">
         <v>85</v>
       </c>
-      <c r="J144" t="s">
-        <v>350</v>
-      </c>
       <c r="K144" s="8">
         <v>18004788111</v>
       </c>
@@ -8668,9 +8235,6 @@
       <c r="I145" t="s">
         <v>85</v>
       </c>
-      <c r="J145" t="s">
-        <v>350</v>
-      </c>
       <c r="K145" s="8">
         <v>18004788111</v>
       </c>
@@ -8715,9 +8279,6 @@
       <c r="I146" t="s">
         <v>85</v>
       </c>
-      <c r="J146" t="s">
-        <v>350</v>
-      </c>
       <c r="K146" s="8">
         <v>18004788111</v>
       </c>
@@ -8762,9 +8323,6 @@
       <c r="I147" t="s">
         <v>85</v>
       </c>
-      <c r="J147" t="s">
-        <v>350</v>
-      </c>
       <c r="K147" s="8">
         <v>18004788111</v>
       </c>
@@ -8809,9 +8367,6 @@
       <c r="I148" t="s">
         <v>85</v>
       </c>
-      <c r="J148" t="s">
-        <v>350</v>
-      </c>
       <c r="K148" s="8">
         <v>18004788111</v>
       </c>
@@ -8856,9 +8411,6 @@
       <c r="I149" t="s">
         <v>85</v>
       </c>
-      <c r="J149" t="s">
-        <v>350</v>
-      </c>
       <c r="K149" s="8">
         <v>18004788111</v>
       </c>
@@ -8903,9 +8455,6 @@
       <c r="I150" t="s">
         <v>85</v>
       </c>
-      <c r="J150" t="s">
-        <v>350</v>
-      </c>
       <c r="K150" s="8">
         <v>18004788111</v>
       </c>
@@ -8950,9 +8499,6 @@
       <c r="I151" t="s">
         <v>85</v>
       </c>
-      <c r="J151" t="s">
-        <v>350</v>
-      </c>
       <c r="K151" s="8">
         <v>18004788111</v>
       </c>
@@ -8997,9 +8543,6 @@
       <c r="I152" t="s">
         <v>85</v>
       </c>
-      <c r="J152" t="s">
-        <v>350</v>
-      </c>
       <c r="K152" s="8">
         <v>18004788111</v>
       </c>
@@ -9044,9 +8587,6 @@
       <c r="I153" t="s">
         <v>85</v>
       </c>
-      <c r="J153" t="s">
-        <v>350</v>
-      </c>
       <c r="K153" s="8">
         <v>18004788111</v>
       </c>
@@ -9091,9 +8631,6 @@
       <c r="I154" t="s">
         <v>85</v>
       </c>
-      <c r="J154" t="s">
-        <v>350</v>
-      </c>
       <c r="K154" s="8">
         <v>18004788111</v>
       </c>
@@ -9138,9 +8675,6 @@
       <c r="I155" t="s">
         <v>85</v>
       </c>
-      <c r="J155" t="s">
-        <v>350</v>
-      </c>
       <c r="K155" s="8">
         <v>18004788111</v>
       </c>
@@ -9185,9 +8719,6 @@
       <c r="I156" t="s">
         <v>85</v>
       </c>
-      <c r="J156" t="s">
-        <v>350</v>
-      </c>
       <c r="K156" s="8">
         <v>18004788111</v>
       </c>
@@ -9232,9 +8763,6 @@
       <c r="I157" t="s">
         <v>85</v>
       </c>
-      <c r="J157" t="s">
-        <v>350</v>
-      </c>
       <c r="K157" s="8">
         <v>18004788111</v>
       </c>
@@ -9279,9 +8807,6 @@
       <c r="I158" t="s">
         <v>85</v>
       </c>
-      <c r="J158" t="s">
-        <v>350</v>
-      </c>
       <c r="K158" s="8">
         <v>18004788111</v>
       </c>
@@ -9326,9 +8851,6 @@
       <c r="I159" t="s">
         <v>85</v>
       </c>
-      <c r="J159" t="s">
-        <v>350</v>
-      </c>
       <c r="K159" s="8">
         <v>18004788111</v>
       </c>
@@ -9373,9 +8895,6 @@
       <c r="I160" t="s">
         <v>85</v>
       </c>
-      <c r="J160" t="s">
-        <v>350</v>
-      </c>
       <c r="K160" s="8">
         <v>18004788111</v>
       </c>
@@ -9420,9 +8939,6 @@
       <c r="I161" t="s">
         <v>85</v>
       </c>
-      <c r="J161" t="s">
-        <v>350</v>
-      </c>
       <c r="K161" s="8">
         <v>18004788111</v>
       </c>
@@ -9467,9 +8983,6 @@
       <c r="I162" t="s">
         <v>85</v>
       </c>
-      <c r="J162" t="s">
-        <v>350</v>
-      </c>
       <c r="K162" s="8">
         <v>18004788111</v>
       </c>
@@ -9514,9 +9027,6 @@
       <c r="I163" t="s">
         <v>86</v>
       </c>
-      <c r="J163" t="s">
-        <v>350</v>
-      </c>
       <c r="K163" s="8">
         <v>17760578425</v>
       </c>
@@ -9561,9 +9071,6 @@
       <c r="I164" t="s">
         <v>86</v>
       </c>
-      <c r="J164" t="s">
-        <v>350</v>
-      </c>
       <c r="K164" s="8">
         <v>17760578425</v>
       </c>
@@ -9608,9 +9115,6 @@
       <c r="I165" t="s">
         <v>86</v>
       </c>
-      <c r="J165" t="s">
-        <v>350</v>
-      </c>
       <c r="K165" s="8">
         <v>17760578425</v>
       </c>
@@ -9655,9 +9159,6 @@
       <c r="I166" t="s">
         <v>86</v>
       </c>
-      <c r="J166" t="s">
-        <v>350</v>
-      </c>
       <c r="K166" s="8">
         <v>17760578425</v>
       </c>
@@ -9702,9 +9203,6 @@
       <c r="I167" t="s">
         <v>86</v>
       </c>
-      <c r="J167" t="s">
-        <v>350</v>
-      </c>
       <c r="K167" s="8">
         <v>17760578425</v>
       </c>
@@ -9749,9 +9247,6 @@
       <c r="I168" t="s">
         <v>86</v>
       </c>
-      <c r="J168" t="s">
-        <v>350</v>
-      </c>
       <c r="K168" s="8">
         <v>17760578425</v>
       </c>
@@ -9796,9 +9291,6 @@
       <c r="I169" t="s">
         <v>86</v>
       </c>
-      <c r="J169" t="s">
-        <v>350</v>
-      </c>
       <c r="K169" s="8">
         <v>17760578425</v>
       </c>
@@ -9843,9 +9335,6 @@
       <c r="I170" t="s">
         <v>86</v>
       </c>
-      <c r="J170" t="s">
-        <v>350</v>
-      </c>
       <c r="K170" s="8">
         <v>17760578425</v>
       </c>
@@ -9890,9 +9379,6 @@
       <c r="I171" t="s">
         <v>86</v>
       </c>
-      <c r="J171" t="s">
-        <v>350</v>
-      </c>
       <c r="K171" s="8">
         <v>17760578425</v>
       </c>
@@ -9937,9 +9423,6 @@
       <c r="I172" t="s">
         <v>86</v>
       </c>
-      <c r="J172" t="s">
-        <v>350</v>
-      </c>
       <c r="K172" s="8">
         <v>17760578425</v>
       </c>
@@ -9984,9 +9467,6 @@
       <c r="I173" t="s">
         <v>86</v>
       </c>
-      <c r="J173" t="s">
-        <v>350</v>
-      </c>
       <c r="K173" s="8">
         <v>17760578425</v>
       </c>
@@ -10031,9 +9511,6 @@
       <c r="I174" t="s">
         <v>86</v>
       </c>
-      <c r="J174" t="s">
-        <v>350</v>
-      </c>
       <c r="K174" s="8">
         <v>17760578425</v>
       </c>
@@ -10078,9 +9555,6 @@
       <c r="I175" t="s">
         <v>86</v>
       </c>
-      <c r="J175" t="s">
-        <v>350</v>
-      </c>
       <c r="K175" s="8">
         <v>17760578425</v>
       </c>
@@ -10125,9 +9599,6 @@
       <c r="I176" t="s">
         <v>86</v>
       </c>
-      <c r="J176" t="s">
-        <v>350</v>
-      </c>
       <c r="K176" s="8">
         <v>17760578425</v>
       </c>
@@ -10172,9 +9643,6 @@
       <c r="I177" t="s">
         <v>86</v>
       </c>
-      <c r="J177" t="s">
-        <v>350</v>
-      </c>
       <c r="K177" s="8">
         <v>17760578425</v>
       </c>
@@ -10219,9 +9687,6 @@
       <c r="I178" t="s">
         <v>86</v>
       </c>
-      <c r="J178" t="s">
-        <v>350</v>
-      </c>
       <c r="K178" s="8">
         <v>17760578425</v>
       </c>
@@ -10266,9 +9731,6 @@
       <c r="I179" t="s">
         <v>86</v>
       </c>
-      <c r="J179" t="s">
-        <v>350</v>
-      </c>
       <c r="K179" s="8">
         <v>17760578425</v>
       </c>
@@ -10313,9 +9775,6 @@
       <c r="I180" t="s">
         <v>86</v>
       </c>
-      <c r="J180" t="s">
-        <v>350</v>
-      </c>
       <c r="K180" s="8">
         <v>17760578425</v>
       </c>
@@ -10360,9 +9819,6 @@
       <c r="I181" t="s">
         <v>86</v>
       </c>
-      <c r="J181" t="s">
-        <v>350</v>
-      </c>
       <c r="K181" s="8">
         <v>17760578425</v>
       </c>
@@ -10407,9 +9863,6 @@
       <c r="I182" t="s">
         <v>86</v>
       </c>
-      <c r="J182" t="s">
-        <v>350</v>
-      </c>
       <c r="K182" s="8">
         <v>17760578425</v>
       </c>
@@ -10454,9 +9907,6 @@
       <c r="I183" t="s">
         <v>86</v>
       </c>
-      <c r="J183" t="s">
-        <v>350</v>
-      </c>
       <c r="K183" s="8">
         <v>17760578425</v>
       </c>
@@ -10501,9 +9951,6 @@
       <c r="I184" t="s">
         <v>86</v>
       </c>
-      <c r="J184" t="s">
-        <v>350</v>
-      </c>
       <c r="K184" s="8">
         <v>17760578425</v>
       </c>
@@ -10548,9 +9995,6 @@
       <c r="I185" t="s">
         <v>86</v>
       </c>
-      <c r="J185" t="s">
-        <v>350</v>
-      </c>
       <c r="K185" s="8">
         <v>17760578425</v>
       </c>
@@ -10595,9 +10039,6 @@
       <c r="I186" t="s">
         <v>86</v>
       </c>
-      <c r="J186" t="s">
-        <v>350</v>
-      </c>
       <c r="K186" s="8">
         <v>17760578425</v>
       </c>
@@ -10642,9 +10083,6 @@
       <c r="I187" t="s">
         <v>86</v>
       </c>
-      <c r="J187" t="s">
-        <v>350</v>
-      </c>
       <c r="K187" s="8">
         <v>17760578425</v>
       </c>
@@ -10689,9 +10127,6 @@
       <c r="I188" t="s">
         <v>86</v>
       </c>
-      <c r="J188" t="s">
-        <v>350</v>
-      </c>
       <c r="K188" s="8">
         <v>17760578425</v>
       </c>
@@ -10736,9 +10171,6 @@
       <c r="I189" t="s">
         <v>86</v>
       </c>
-      <c r="J189" t="s">
-        <v>350</v>
-      </c>
       <c r="K189" s="8">
         <v>17760578425</v>
       </c>
@@ -10783,9 +10215,6 @@
       <c r="I190" t="s">
         <v>86</v>
       </c>
-      <c r="J190" t="s">
-        <v>350</v>
-      </c>
       <c r="K190" s="8">
         <v>17760578425</v>
       </c>
@@ -10830,9 +10259,6 @@
       <c r="I191" t="s">
         <v>86</v>
       </c>
-      <c r="J191" t="s">
-        <v>350</v>
-      </c>
       <c r="K191" s="8">
         <v>17760578425</v>
       </c>
@@ -10877,9 +10303,6 @@
       <c r="I192" t="s">
         <v>86</v>
       </c>
-      <c r="J192" t="s">
-        <v>350</v>
-      </c>
       <c r="K192" s="8">
         <v>17760578425</v>
       </c>
@@ -10924,9 +10347,6 @@
       <c r="I193" t="s">
         <v>86</v>
       </c>
-      <c r="J193" t="s">
-        <v>350</v>
-      </c>
       <c r="K193" s="8">
         <v>17760578425</v>
       </c>
@@ -10971,9 +10391,6 @@
       <c r="I194" t="s">
         <v>86</v>
       </c>
-      <c r="J194" t="s">
-        <v>350</v>
-      </c>
       <c r="K194" s="8">
         <v>17760578425</v>
       </c>
@@ -11017,9 +10434,6 @@
       </c>
       <c r="I195" t="s">
         <v>86</v>
-      </c>
-      <c r="J195" t="s">
-        <v>350</v>
       </c>
       <c r="K195" s="8">
         <v>17760578425</v>
